--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -5538,6 +5538,151 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5571,7 +5716,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5799,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -5664,7 +5809,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -5716,7 +5861,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -5683,6 +5683,151 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5716,7 +5861,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5944,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -5809,7 +5954,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -5861,7 +6006,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -5828,6 +5828,151 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5861,7 +6006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5944,7 +6089,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5954,7 +6099,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -6006,7 +6151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -5973,6 +5973,151 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" t="n">
+        <v>6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6006,7 +6151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6234,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6099,7 +6244,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -6151,7 +6296,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -6118,6 +6118,151 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6151,7 +6296,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6379,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6244,7 +6389,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -6296,7 +6441,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -6263,6 +6263,151 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>6</v>
+      </c>
+      <c r="O40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6296,7 +6441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6524,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -6389,7 +6534,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -6441,7 +6586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d136/2026-2029.xlsx
+++ b/diseases/d136/2026-2029.xlsx
@@ -33702,6 +33702,582 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>JP-01</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Hokkaido, Japan</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="n">
+        <v>1</v>
+      </c>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AT230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>JP-07</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Fukushima, Japan</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="n">
+        <v>1</v>
+      </c>
+      <c r="P231" t="n">
+        <v>1</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>JP-11</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Saitama, Japan</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>1</v>
+      </c>
+      <c r="P232" t="n">
+        <v>1</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>chlamydial-pneumonia</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>JP-26</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Kyoto, Japan</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D136</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Chlamydial pneumonia</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>衣原体肺炎</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" t="n">
+        <v>1</v>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f70d0f8bd99b9bfbfaafebbbd002</t>
+        </is>
+      </c>
+      <c r="AT233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33735,7 +34311,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -33818,7 +34394,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -33828,7 +34404,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -33880,7 +34456,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16">
